--- a/docs/사용자요구사항분석표.xlsx
+++ b/docs/사용자요구사항분석표.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>데이터 담당</t>
+          <t>구본국(데이터 담당)</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>개발팀</t>
+          <t>김동진(백엔드 담당)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
